--- a/output/2026-09-30_20_Malesia_Johor_ATEX_Equipment_Services.xlsx
+++ b/output/2026-09-30_20_Malesia_Johor_ATEX_Equipment_Services.xlsx
@@ -673,7 +673,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verificato tramite pagina ufficiale 'Contact Us - Branch (JB)' del sito aziendale, che conferma sede operativa a Johor Bahru (No. 5, Jalan Banang Satu, Taman Johor Industrial Estate, 81200 Johor Bahru). Telefono indicato per la filiale JB (prefisso 06, condiviso con altre sedi aziendali).</t>
+          <t>Verificato tramite pagina ufficiale 'Contact Us - Branch (JB)' del sito aziendale, che conferma sede operativa a Johor Bahru (No. 5, Jalan Banang Satu, Taman Johor Industrial Estate, 81200 Johor Bahru). Telefono indicato per la filiale JB (prefisso 06, condiviso con altre sedi aziendali). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale (pagina prodotto vacuum cleaner ATEX). Azienda principalmente generalista di forniture per pulizia industriale; la linea ATEX e' di nicchia ma effettivamente rivenduta (non e' un utilizzatore finale).</t>
+          <t>Verificato tramite sito ufficiale (pagina prodotto vacuum cleaner ATEX). Azienda principalmente generalista di forniture per pulizia industriale; la linea ATEX e' di nicchia ma effettivamente rivenduta (non e' un utilizzatore finale). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale (categoria 'Explosion Proof': buzzer, hand lamp, LED fitting, push button) e newpages.com.my. Indirizzo: 56, Jalan Rosmerah 2/17, Taman Johor Jaya, 81100 Johor Bahru.</t>
+          <t>Verificato tramite sito ufficiale (categoria 'Explosion Proof': buzzer, hand lamp, LED fitting, push button) e newpages.com.my. Indirizzo: 56, Jalan Rosmerah 2/17, Taman Johor Jaya, 81100 Johor Bahru. [DUPLICATO — vedi anche: 2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">

--- a/output/2026-09-30_20_Malesia_Johor_ATEX_Equipment_Services.xlsx
+++ b/output/2026-09-30_20_Malesia_Johor_ATEX_Equipment_Services.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
